--- a/outputs/BOM_REVIEW.xlsx
+++ b/outputs/BOM_REVIEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI102"/>
+  <dimension ref="A1:AH102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,25 +569,20 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>判別比例</t>
+          <t>NER_Used</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>NER_Used</t>
+          <t>status</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>review_reason</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
-        <is>
-          <t>review_reason</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
         <is>
           <t>NER_Result</t>
         </is>
@@ -680,25 +675,22 @@
           <t>RESR05%1/10W0603</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>1.25</v>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('5', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -799,25 +791,22 @@
           <t>CAP47425V10%0603X7R</t>
         </is>
       </c>
-      <c r="AE3" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), ('470nF', 'Capacitance'), ('(', 'IGNORE'), ('0.47uF', 'Capacitance'), (')', 'IGNORE'), ('25V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -907,25 +896,22 @@
           <t>OT3.3V480MHz2Mb</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>0.4794520547945205</v>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('MCU', 'Category'), ('STM32H743VI', 'O'), ('3.3V', 'Voltage'), ('32bit', 'O'), ('Arm', 'Category'), ('®', 'O'), ('Cortex', 'O'), ('®', 'O'), ('-', 'O'), ('M7', 'O'), ('480MHz', 'Frequency'), ('2Mb', 'Pin_Count'), ('flash', 'O'), ('512Kb', 'O'), ('SRMA', 'O'), ('LQFP100', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1002,25 +988,22 @@
           <t>ICSOT-23-5</t>
         </is>
       </c>
-      <c r="AE5" t="n">
-        <v>0.5</v>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('SINGLE', 'O'), ('INVERTER', 'O'), ('-', 'O'), ('GATEt', 'O'), ('SOT', 'Package'), ('-', 'Package'), ('23', 'Package'), ('-', 'Package'), ('5', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1098,25 +1081,22 @@
           <t>ICWQFN16</t>
         </is>
       </c>
-      <c r="AE6" t="n">
-        <v>0.3947368421052632</v>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('DAC', 'O'), ('OCTAL', 'O'), ('16', 'O'), ('-', 'O'), ('Bit', 'O'), ('DAC80508Z', 'O'), ('SPI', 'O'), ('WQFN16', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1193,25 +1173,22 @@
           <t>ICSOT-23-5</t>
         </is>
       </c>
-      <c r="AE7" t="n">
-        <v>0.53125</v>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('CHARGE', 'O'), ('PUMP', 'O'), ('INVERTER', 'O'), ('SOT', 'Package'), ('-', 'Package'), ('23', 'Package'), ('-', 'Package'), ('5', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1292,25 +1269,22 @@
           <t>IC166MHzWSON6</t>
         </is>
       </c>
-      <c r="AE8" t="n">
-        <v>0.3225806451612903</v>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_4/13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
-        <is>
-          <t>ner_low_valid_4/13</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('S25HL512TFANH', 'O'), ('512Mbit', 'O'), ('166MHz', 'Frequency'), ('SDR', 'O'), ('FLASH', 'O'), ('SPI', 'O'), ('/', 'O'), ('QUAD', 'O'), ('Industrial', 'O'), ('WSON6', 'O'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1411,25 +1385,22 @@
           <t>CAP22425V10%0603X7R</t>
         </is>
       </c>
-      <c r="AE9" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), ('220nF', 'Capacitance'), ('(', 'IGNORE'), ('0.22uF', 'Capacitance'), (')', 'IGNORE'), ('25V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1526,25 +1497,22 @@
           <t>RES100R1%1/10W0603</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1.25</v>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), ('100', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('≦', 'Temp_Coefficient'), ('50ppm', 'Temp_Coefficient'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('0603', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1645,25 +1613,22 @@
           <t>CAP105100V10%1206X7R</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1.222222222222222</v>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('1uF', 'Capacitance'), ('(', 'IGNORE'), ('1000nF', 'Capacitance'), (')', 'IGNORE'), ('100V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('1206', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1749,25 +1714,22 @@
           <t>IC5.5V400kHzSOIC-8</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>0.5434782608695652</v>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('EEPROM', 'O'), ('24LC512', 'O'), ('512KBIT', 'O'), ('400kHz', 'Frequency'), ('2.5', 'O'), ('~', 'O'), ('5.5V', 'Voltage'), ('SOIC', 'Package'), ('-', 'Package'), ('8', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1856,25 +1818,22 @@
           <t>OT1.71~3.6V512Kbyte</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>0.6753246753246753</v>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('MCU', 'Category'), ('ARM', 'Category'), ('STM32G474VET3', 'O'), ('1.71', 'Voltage'), ('~', 'Voltage'), ('3.6V', 'Voltage'), ('512Kbyte', 'Voltage'), ('32Bit', 'O'), ('170MHz', 'Frequency'), ('213DMIPS', 'O'), ('128KB', 'O'), ('SRAM', 'O'), ('LQFP100', 'Package'), ('(', 'IGNORE'), ('14x14mm', 'Size'), (')', 'IGNORE'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -1955,25 +1914,22 @@
           <t>OT1x5P2.0mm</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>0.6222222222222222</v>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('Female', 'O'), ('Header', 'Category'), ('Straight', 'O'), ('1x5P', 'Pin_Count'), ('2.0mm', 'Size'), ('Black', 'Color'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2066,25 +2022,22 @@
           <t>RESR05%1/8W0805</t>
         </is>
       </c>
-      <c r="AE15" t="n">
-        <v>1.263157894736842</v>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('8W', 'Power'), ('5', 'Tolerance'), ('%', 'Tolerance'), ('0805', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2185,25 +2138,22 @@
           <t>CAP22550V10%0805X7R</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('2.2uF', 'Capacitance'), ('50V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0805', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2282,25 +2232,22 @@
           <t>OT1x2P2.0mm</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>0.6571428571428571</v>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('HEADER', 'Category'), ('TOP', 'O'), ('-', 'O'), ('ENTRY', 'O'), ('1x2P', 'Pin_Count'), ('2.0mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2381,25 +2328,22 @@
           <t>IC5VSOIC-8</t>
         </is>
       </c>
-      <c r="AE18" t="n">
-        <v>0.5666666666666667</v>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('VOLT', 'O'), ('REFERENCE', 'O'), ('LDO', 'O'), ('5V', 'Voltage'), ('SOIC', 'Package'), ('-', 'Package'), ('8', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2492,25 +2436,22 @@
           <t>RES1K01%1/10W0603</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1.285714285714286</v>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('1K', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2600,25 +2541,22 @@
           <t>OT3.3V480MHz2Mb</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>0.4794520547945205</v>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('MCU', 'Category'), ('STM32H743BI', 'O'), ('3.3V', 'Voltage'), ('32bit', 'O'), ('Arm', 'Category'), ('®', 'O'), ('Cortex', 'O'), ('®', 'O'), ('-', 'O'), ('M7', 'O'), ('480MHz', 'Frequency'), ('2Mb', 'Pin_Count'), ('flash', 'O'), ('512Kb', 'O'), ('SRMA', 'O'), ('LQFP208', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2699,25 +2637,22 @@
           <t>OT5.5V</t>
         </is>
       </c>
-      <c r="AE21" t="n">
-        <v>0.625</v>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
         <is>
           <t>[('Logic', 'Category'), ('IC', 'Category'), ('SN74LVC2G125', 'Package'), ('Dual', 'O'), ('BUF', 'O'), ('NON', 'O'), ('-', 'O'), ('INVERT', 'O'), ('5.5V', 'Voltage'), ('3', 'O'), ('-', 'O'), ('state', 'O'), ('SM8', 'Package'), ('-', 'Package'), ('8', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2803,25 +2738,22 @@
           <t>IC5.5V</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>0.6739130434782609</v>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
         <is>
           <t>[('Logic', 'O'), ('IC', 'Category'), ('SN74LVC1G34', 'Package'), ('BUF', 'O'), ('NON', 'O'), ('-', 'O'), ('INVERT', 'O'), ('5.5V', 'Voltage'), ('SOT', 'Package'), ('-', 'Package'), ('235', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -2914,25 +2846,22 @@
           <t>RES100R1%1/10W0603</t>
         </is>
       </c>
-      <c r="AE23" t="n">
-        <v>1.318181818181818</v>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('100', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3010,25 +2939,22 @@
           <t>ICWQFN16</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>0.3947368421052632</v>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('DAC', 'O'), ('OCTAL', 'O'), ('14', 'O'), ('-', 'O'), ('Bit', 'O'), ('DAC70508Z', 'O'), ('SPI', 'O'), ('WQFN16', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3129,25 +3055,22 @@
           <t>CAP22450V10%0603X7R</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), ('220nF', 'Capacitance'), ('(', 'IGNORE'), ('0.22uF', 'Capacitance'), (')', 'IGNORE'), ('50V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3228,25 +3151,22 @@
           <t>OT100Kψ6mm</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>0.8</v>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('Variable', 'O'), ('Resistor', 'Category'), ('100K', 'Resistance'), ('Ω', 'Resistance'), ('ψ', 'Size'), ('6mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3335,25 +3255,22 @@
           <t>OT1.71~3.6V512Kbyte</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>0.6753246753246753</v>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('MCU', 'Category'), ('ARM', 'Category'), ('STM32G474VET6', 'O'), ('1.71', 'Voltage'), ('~', 'Voltage'), ('3.6V', 'Voltage'), ('512Kbyte', 'Voltage'), ('32Bit', 'O'), ('170MHz', 'Frequency'), ('213DMIPS', 'O'), ('128KB', 'O'), ('SRAM', 'O'), ('LQFP100', 'Package'), ('(', 'IGNORE'), ('14x14mm', 'Size'), (')', 'IGNORE'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3430,25 +3347,22 @@
           <t>OT3.3V</t>
         </is>
       </c>
-      <c r="AE28" t="n">
-        <v>0.5222222222222223</v>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
         <is>
           <t>[('Module', 'Category'), ('BRIDGE', 'Category'), ('ETHR', 'O'), ('RS232', 'O'), ('to', 'O'), ('TCP', 'O'), ('/', 'O'), ('IP', 'O'), ('10', 'O'), ('/', 'O'), ('100', 'O'), ('BASE', 'O'), ('-', 'O'), ('T', 'O'), ('/', 'O'), ('TX', 'O'), ('PHY', 'O'), ('3.3V', 'Voltage'), ('Ethernet', 'Category'), ('transformer', 'O'), ('34.00', 'Size'), ('×', 'Size'), ('24.00', 'Size'), ('×', 'Size'), ('12.40mm', 'Size'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3529,25 +3443,22 @@
           <t>OT3.0</t>
         </is>
       </c>
-      <c r="AE29" t="n">
-        <v>0.7540983606557377</v>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=5</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
-        <is>
-          <t>short_display20_len=5</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('Type', 'Type'), ('A', 'O'), ('USB', 'Category'), ('3.0', 'Voltage'), ('Receptacle', 'Category'), ('Dual', 'O'), ('Stacked', 'O'), ('VERT', 'O'), ('17.88x14.5x15.62mm', 'Size'), ('DIP', 'O'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3620,25 +3531,22 @@
           <t>OT2X12P</t>
         </is>
       </c>
-      <c r="AE30" t="n">
-        <v>0.7307692307692307</v>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('HEADER', 'Category'), (',', 'IGNORE'), ('VERT', 'O'), ('2X12P', 'Pin_Count'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3715,25 +3623,22 @@
           <t>OT10-</t>
         </is>
       </c>
-      <c r="AE31" t="n">
-        <v>0.3333333333333333</v>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_6/20</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
-        <is>
-          <t>ner_low_valid_6/20</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('RTC', 'O'), ('IC', 'Category'), ('Clock', 'O'), ('/', 'O'), ('Calendar', 'O'), ('I', 'O'), ('²', 'O'), ('C', 'O'), (',', 'IGNORE'), ('2', 'O'), ('-', 'O'), ('Wire', 'O'), ('Serial', 'O'), ('10', 'Package'), ('-', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3814,25 +3719,22 @@
           <t>OT16V2A</t>
         </is>
       </c>
-      <c r="AE32" t="n">
-        <v>0.5333333333333333</v>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
         <is>
           <t>[('FUSE', 'Category'), ('PTC', 'O'), ('RESETTABLE', 'O'), ('16V', 'Voltage'), ('2A', 'Current'), ('1812', 'O'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3905,25 +3807,22 @@
           <t>IC</t>
         </is>
       </c>
-      <c r="AE33" t="n">
-        <v>0.6</v>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('LDO', 'O'), ('REG', 'O'), ('ADJ', 'O'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -3996,25 +3895,22 @@
           <t>OT</t>
         </is>
       </c>
-      <c r="AE34" t="n">
-        <v>0.78</v>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
         <is>
           <t>[('ENCODER', 'Category'), (',', 'IGNORE'), ('Rotary', 'O'), ('ED1115S', 'O'), ('KC', 'Type'), ('/', 'Type'), ('LAL', 'Type'), ('type', 'Type'), ('Vertical', 'Type'), ('with', 'O'), ('Push', 'Type'), ('-', 'O'), ('on', 'O'), ('Switch', 'Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4095,25 +3991,22 @@
           <t>OT2.54mm</t>
         </is>
       </c>
-      <c r="AE35" t="n">
-        <v>0.9795918367346939</v>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
         <is>
           <t>[('LED', 'Category'), ('DIA', 'O'), ('LAMP', 'Category'), ('Yellow', 'Color'), ('/', 'Color'), ('Green', 'Color'), ('φ', 'O'), ('3', 'O'), ('3.85x4.30mm', 'Size'), ('P', 'Size'), ('=', 'Size'), ('2.54mm', 'Size'), ('DIP', 'O'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4190,25 +4083,22 @@
           <t>IC5.5V</t>
         </is>
       </c>
-      <c r="AE36" t="n">
-        <v>0.7111111111111111</v>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('SN74LV1T125DBVR', 'Package'), ('BUF', 'O'), ('NON', 'O'), ('-', 'O'), ('INVERT', 'O'), ('5.5V', 'Voltage'), ('SOT', 'Package'), ('-', 'Package'), ('235', 'Package'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4289,25 +4179,22 @@
           <t>IC18R/1</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>0.2826086956521739</v>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('MAX13487EESA', 'O'), ('+', 'O'), ('Limited', 'O'), ('TRANSCEIVER', 'O'), ('HALF', 'O'), ('1', 'Resistance'), ('/', 'Power'), ('1', 'Power'), ('8SO', 'Resistance'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4384,25 +4271,22 @@
           <t>OT3.5mmPHONE JACK</t>
         </is>
       </c>
-      <c r="AE38" t="n">
-        <v>0.6666666666666666</v>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('PHONE', 'Type'), ('JACK', 'Type'), ('PJ', 'O'), ('-', 'O'), ('3896', 'O'), ('Ø', 'O'), ('3.5mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4481,25 +4365,22 @@
           <t>OT1x5P2.0mm</t>
         </is>
       </c>
-      <c r="AE39" t="n">
-        <v>0.6571428571428571</v>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('HEADER', 'Category'), ('TOP', 'O'), ('-', 'O'), ('ENTRY', 'O'), ('1x5P', 'Pin_Count'), ('2.0mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4580,25 +4461,22 @@
           <t>OT100Kψ6mm</t>
         </is>
       </c>
-      <c r="AE40" t="n">
-        <v>0.8</v>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('Variable', 'O'), ('Resistor', 'Category'), ('100K', 'Resistance'), ('Ω', 'Resistance'), ('ψ', 'Size'), ('6mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4679,25 +4557,22 @@
           <t>OT3.5mmPHONE JACK</t>
         </is>
       </c>
-      <c r="AE41" t="n">
-        <v>0.9642857142857143</v>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('PHONE', 'Type'), ('JACK', 'Type'), ('Ø', 'O'), ('3.5mm', 'Size'), ('Black', 'Color'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4796,25 +4671,22 @@
           <t>RESR05%1/10W0603</t>
         </is>
       </c>
-      <c r="AE42" t="n">
-        <v>1.25</v>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('5', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -4913,25 +4785,22 @@
           <t>RESR05%1/8W0805</t>
         </is>
       </c>
-      <c r="AE43" t="n">
-        <v>1.263157894736842</v>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('8W', 'Power'), ('5', 'Tolerance'), ('%', 'Tolerance'), ('0805', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5008,25 +4877,22 @@
           <t>ICTSSOP-16</t>
         </is>
       </c>
-      <c r="AE44" t="n">
-        <v>0.3777777777777778</v>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('CMOS', 'O'), ('8', 'O'), ('-', 'O'), ('Channel', 'O'), ('Multiplexers', 'O'), ('ADG708', 'O'), ('TSSOP', 'Package'), ('-', 'Package'), ('16', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5129,25 +4995,22 @@
           <t>CAP22450V10%0603X7R</t>
         </is>
       </c>
-      <c r="AE45" t="n">
-        <v>1.206896551724138</v>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('0.22uF', 'Capacitance'), ('50V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5230,25 +5093,22 @@
           <t>OT1206</t>
         </is>
       </c>
-      <c r="AE46" t="n">
-        <v>1.1875</v>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
         <is>
           <t>[('LED', 'Category'), (',', 'IGNORE'), ('GREEN', 'Color'), ('1206', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5325,25 +5185,22 @@
           <t>OT2X8P2.0mm</t>
         </is>
       </c>
-      <c r="AE47" t="n">
-        <v>0.8214285714285714</v>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('HEADER', 'Category'), (',', 'IGNORE'), ('RA', 'O'), ('2X8P', 'Pin_Count'), ('2.0mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5414,25 +5271,22 @@
           <t>OT</t>
         </is>
       </c>
-      <c r="AE48" t="n">
-        <v>0.5</v>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('TEST', 'O'), ('_', 'O'), ('POINT', 'O'), ('BLACK', 'Color'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5518,25 +5372,22 @@
           <t>IC5.5V400kHzSOIC-8</t>
         </is>
       </c>
-      <c r="AE49" t="n">
-        <v>0.5434782608695652</v>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('EEPROM', 'O'), ('24LC512', 'O'), ('512KBIT', 'O'), ('400kHz', 'Frequency'), ('2.5', 'O'), ('~', 'O'), ('5.5V', 'Voltage'), ('SOIC', 'Package'), ('-', 'Package'), ('8', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5613,25 +5464,22 @@
           <t>OT128KBLQFP-64</t>
         </is>
       </c>
-      <c r="AE50" t="n">
-        <v>0.525</v>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('MCU', 'Category'), ('STM32F072', 'O'), ('32BIT', 'O'), ('128KB', 'Pin_Count'), ('FLASH', 'O'), ('LQFP', 'Package'), ('-', 'Package'), ('64', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5716,25 +5564,22 @@
           <t>IC2.93V20mASOT-143</t>
         </is>
       </c>
-      <c r="AE51" t="n">
-        <v>0.3968253968253968</v>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('Supervisory', 'O'), ('Manual', 'O'), ('Reset', 'O'), ('Input', 'O'), ('SGM811', 'O'), ('-', 'O'), ('SXKA4', 'O'), ('/', 'O'), ('TR', 'O'), ('2.93V', 'Voltage'), ('20mA', 'Current'), ('SOT', 'Package'), ('-', 'Package'), ('143', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5815,25 +5660,22 @@
           <t>OT6V2.6A</t>
         </is>
       </c>
-      <c r="AE52" t="n">
-        <v>0.8095238095238095</v>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
         <is>
           <t>[('FUSE', 'Category'), (',', 'IGNORE'), ('PTC', 'O'), ('6V', 'Voltage'), ('2.6A', 'Current'), ('1812', 'O'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -5911,25 +5753,22 @@
           <t>ICTSSOP-14</t>
         </is>
       </c>
-      <c r="AE53" t="n">
-        <v>0.6071428571428571</v>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('QUAD', 'O'), ('2', 'O'), ('-', 'O'), ('IN', 'O'), ('OR', 'O'), ('GATE', 'O'), ('TSSOP', 'Package'), ('-', 'Package'), ('14', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6010,25 +5849,22 @@
           <t>IC5VSOIC-8</t>
         </is>
       </c>
-      <c r="AE54" t="n">
-        <v>0.5666666666666667</v>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('VOLT', 'O'), ('REFERENCE', 'O'), ('LDO', 'O'), ('5V', 'Voltage'), ('SOIC', 'Package'), ('-', 'Package'), ('8', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6105,25 +5941,22 @@
           <t>ICTSSOP-14</t>
         </is>
       </c>
-      <c r="AE55" t="n">
-        <v>0.53125</v>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('LOGARITHM', 'O'), ('CONV', 'O'), ('160DB', 'O'), ('TSSOP', 'Package'), ('-', 'Package'), ('14', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6218,25 +6051,22 @@
           <t>RESR21%1/2W1206</t>
         </is>
       </c>
-      <c r="AE56" t="n">
-        <v>1.238095238095238</v>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0.2', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('2W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('1206', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6313,25 +6143,22 @@
           <t>OTLQFP100</t>
         </is>
       </c>
-      <c r="AE57" t="n">
-        <v>0.3454545454545455</v>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('STM32L475VE', 'O'), ('MCU', 'Category'), ('+', 'O'), ('FPU', 'O'), ('32bit', 'O'), ('512KB', 'O'), ('flash', 'O'), ('128KB', 'O'), ('/', 'O'), ('SRAM', 'O'), ('LQFP100', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6416,25 +6243,22 @@
           <t>IC2.93V20mASOT-143</t>
         </is>
       </c>
-      <c r="AE58" t="n">
-        <v>0.4464285714285715</v>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), ('Supervisory', 'O'), ('Manual', 'O'), ('Reset', 'O'), ('Input', 'O'), ('SGM811B', 'O'), ('2.93V', 'Voltage'), ('20mA', 'Current'), ('SOT', 'Package'), ('-', 'Package'), ('143', 'Package'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6516,25 +6340,22 @@
           <t>OT16V6A</t>
         </is>
       </c>
-      <c r="AE59" t="n">
-        <v>0.64</v>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
         <is>
           <t>[('PTC', 'O'), ('RESET', 'O'), ('FUSE', 'Category'), ('16V', 'Voltage'), ('6A', 'Current'), ('2920', 'O'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6619,25 +6440,22 @@
           <t>OT1x4P2.54mm</t>
         </is>
       </c>
-      <c r="AE60" t="n">
-        <v>0.98</v>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('Header', 'Category'), ('1x4P', 'Pin_Count'), ('Right', 'Type'), ('angle', 'Type'), ('P', 'Size'), ('=', 'Size'), ('2.54mm', 'Size'), ('H', 'Size'), ('=', 'Size'), ('6.6mm', 'Size'), ('Gold', 'O'), ('DIP', 'O'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6718,25 +6536,22 @@
           <t>OT9P</t>
         </is>
       </c>
-      <c r="AE61" t="n">
-        <v>0.5454545454545454</v>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=4</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
-        <is>
-          <t>short_display20_len=4</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('D', 'Category'), ('-', 'O'), ('SUB', 'O'), ('9P', 'Pin_Count'), ('FEMALE', 'O'), ('RA', 'O'), ('Black', 'Color'), ('Female', 'O'), ('Screwlock', 'O'), ('(', 'IGNORE'), ('4', 'O'), ('-', 'O'), ('40', 'O'), (')', 'IGNORE'), ('30.81x13.575x20.65mm', 'Size'), ('DIP', 'O'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6829,25 +6644,22 @@
           <t>RESR221%1/2W1210</t>
         </is>
       </c>
-      <c r="AE62" t="n">
-        <v>1.272727272727273</v>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('220m', 'Resistance'), ('Ω', 'Resistance'), ('(', 'IGNORE'), ('0.22', 'Resistance'), ('Ω', 'Resistance'), (')', 'IGNORE'), ('1', 'Power'), ('/', 'Power'), ('2W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('1210', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -6924,25 +6736,22 @@
           <t>OT128KBLQFP-64</t>
         </is>
       </c>
-      <c r="AE63" t="n">
-        <v>0.525</v>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('MCU', 'Category'), ('STM32F072', 'O'), ('32BIT', 'O'), ('128KB', 'Pin_Count'), ('FLASH', 'O'), ('LQFP', 'Package'), ('-', 'Package'), ('64', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7023,25 +6832,22 @@
           <t>OT6V2.6A</t>
         </is>
       </c>
-      <c r="AE64" t="n">
-        <v>0.6071428571428571</v>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
         <is>
           <t>[('FUSE', 'Category'), ('Resettable', 'O'), ('6V', 'Voltage'), ('2.6A', 'Current'), ('2920', 'O'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7110,25 +6916,22 @@
           <t>OT</t>
         </is>
       </c>
-      <c r="AE65" t="n">
-        <v>0.5217391304347826</v>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('OCTAL', 'O'), ('BUFFER', 'Category'), (',', 'IGNORE'), ('3', 'O'), ('STATE', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7201,25 +7004,22 @@
           <t>IC</t>
         </is>
       </c>
-      <c r="AE66" t="n">
-        <v>0.391304347826087</v>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_3/11</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
-        <is>
-          <t>ner_low_valid_3/11</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('BUS', 'O'), ('BUFF', 'O'), ('TRI', 'O'), ('-', 'O'), ('ST', 'O'), ('QUAD', 'O'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7296,25 +7096,22 @@
           <t>ICTSSOP-16</t>
         </is>
       </c>
-      <c r="AE67" t="n">
-        <v>0.6071428571428571</v>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('MULTIPLEXER', 'O'), ('8X1', 'O'), ('TSSOP', 'Package'), ('-', 'Package'), ('16', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7415,25 +7212,22 @@
           <t>RESR21%1/2W1206</t>
         </is>
       </c>
-      <c r="AE68" t="n">
-        <v>1.178571428571429</v>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0.2', 'Resistance'), ('Ω', 'Resistance'), ('(', 'IGNORE'), ('200m', 'Resistance'), ('Ω', 'Resistance'), (')', 'IGNORE'), ('1', 'Power'), ('/', 'Power'), ('2W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('1206', 'Package'), ('&lt;', 'Temp_Coefficient'), ('100ppm', 'Temp_Coefficient'), ('SMD', 'Process_Type'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7506,25 +7300,22 @@
           <t>OT2x6P</t>
         </is>
       </c>
-      <c r="AE69" t="n">
-        <v>0.6666666666666666</v>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('HEADER', 'Category'), ('FEMALE', 'O'), ('2x6P', 'Pin_Count'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7613,25 +7404,22 @@
           <t>OT50V3A5P</t>
         </is>
       </c>
-      <c r="AE70" t="n">
-        <v>0.4705882352941176</v>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('NC5FAH', 'O'), ('Female', 'O'), ('5P', 'Pin_Count'), ('3A', 'Current'), ('&lt;', 'Temp_Coefficient'), ('50V', 'Voltage'), ('Gold', 'O'), ('contact', 'O'), ('Latch', 'O'), ('lock', 'O'), ('25.3x28.8x22.2mm', 'Size'), ('IP40', 'O'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7720,25 +7508,22 @@
           <t>OT50V3A5P</t>
         </is>
       </c>
-      <c r="AE71" t="n">
-        <v>0.4848484848484849</v>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), ('NC5MAH', 'O'), ('Male', 'O'), ('5P', 'Pin_Count'), ('3A', 'Current'), ('&lt;', 'Temp_Coefficient'), ('50V', 'Voltage'), ('Gold', 'O'), ('contact', 'O'), ('Latch', 'O'), ('lock', 'O'), ('25.3x28.8x22.4mm', 'Size'), ('IP40', 'O'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7803,25 +7588,22 @@
           <t>OT3.2mm</t>
         </is>
       </c>
-      <c r="AE72" t="n">
-        <v>0.3333333333333333</v>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_1/7</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
-        <is>
-          <t>ner_low_valid_1/7</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
         <is>
           <t>[('DOUBLE', 'O'), ('TAPE', 'O'), ('60', 'O'), ('*', 'O'), ('45', 'O'), ('*', 'O'), ('3.2mm', 'Size')]</t>
         </is>
@@ -7894,25 +7676,22 @@
           <t>OTLQFP100</t>
         </is>
       </c>
-      <c r="AE73" t="n">
-        <v>0.5277777777777778</v>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('MCU', 'Category'), ('ARM', 'Category'), ('LPC1764', 'O'), ('128KB', 'O'), ('FLASH', 'O'), ('LQFP100', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -7989,25 +7768,22 @@
           <t>OT5</t>
         </is>
       </c>
-      <c r="AE74" t="n">
-        <v>0.303030303030303</v>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_3/14</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
-        <is>
-          <t>ner_low_valid_3/14</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('MICUSB', 'O'), ('-', 'O'), ('5BF', 'Capacitance'), ('-', 'O'), ('2.0', 'O'), ('-', 'O'), ('SD', 'O'), ('-', 'O'), ('S108', 'O'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8076,25 +7852,22 @@
           <t>OT</t>
         </is>
       </c>
-      <c r="AE75" t="n">
-        <v>0.4166666666666667</v>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('FLASH', 'O'), ('MX25L3206E', 'O'), ('with', 'O'), ('code', 'O'), ('for', 'O'), ('Kessil', 'O'), ('Controller', 'Category'), ('RoHS', 'Compliance'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8172,25 +7945,22 @@
           <t>OTsteel</t>
         </is>
       </c>
-      <c r="AE76" t="n">
-        <v>0.6666666666666666</v>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
         <is>
           <t>[('STDOFF', 'O'), (',', 'IGNORE'), ('Carbon', 'O'), ('steel', 'Type'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8259,25 +8029,22 @@
           <t>OT</t>
         </is>
       </c>
-      <c r="AE77" t="n">
-        <v>0.3214285714285715</v>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('PIC', 'O'), ('MCU', 'Category'), ('128KB', 'O'), ('FLASH', 'O'), ('TQFP44', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8350,25 +8117,22 @@
           <t>ICSSOP28</t>
         </is>
       </c>
-      <c r="AE78" t="n">
-        <v>0.4444444444444444</v>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_3/10</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
-        <is>
-          <t>ner_low_valid_3/10</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('I', 'O'), ('/', 'O'), ('O', 'O'), ('EXPANDER', 'O'), ('16Bit', 'O'), ('SSOP28', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8441,25 +8205,22 @@
           <t>OTSOP-16</t>
         </is>
       </c>
-      <c r="AE79" t="n">
-        <v>0.44</v>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('RT8480', 'O'), ('Hight', 'O'), ('Voltage', 'O'), ('Boost', 'O'), ('/', 'O'), ('SEPIC', 'O'), ('Controller', 'Category'), ('SOP', 'Package'), ('-', 'Package'), ('16', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8546,25 +8307,22 @@
           <t>OT2X6P2.0mm</t>
         </is>
       </c>
-      <c r="AE80" t="n">
-        <v>0.9791666666666666</v>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('Wire', 'Category'), ('To', 'O'), ('Board', 'Category'), ('Right', 'Type'), ('Angle', 'Type'), ('K', 'Type'), ('-', 'Type'), ('TYPE', 'Type'), ('2X6P', 'Pin_Count'), ('2.0mm', 'Size'), ('White', 'Color'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8647,25 +8405,22 @@
           <t>OT2X8P2.0mm</t>
         </is>
       </c>
-      <c r="AE81" t="n">
-        <v>0.9767441860465116</v>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('Wire', 'Category'), ('To', 'O'), ('Board', 'Category'), ('Right', 'Type'), ('Angle', 'Type'), ('K', 'Type'), ('-', 'Type'), ('TYPE', 'Type'), ('2X8P', 'Pin_Count'), ('2.0mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8746,25 +8501,22 @@
           <t>OT1x4P2.54mm</t>
         </is>
       </c>
-      <c r="AE82" t="n">
-        <v>0.7777777777777778</v>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('Wafer', 'O'), ('Right', 'Type'), ('Angle', 'Type'), ('(', 'IGNORE'), ('turn', 'O'), ('right', 'O'), (')', 'IGNORE'), ('1x4P', 'Pin_Count'), ('2.54mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8851,25 +8603,22 @@
           <t>OT2X6P2.0mm</t>
         </is>
       </c>
-      <c r="AE83" t="n">
-        <v>0.8636363636363636</v>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('Wire', 'Category'), ('To', 'O'), ('Board', 'O'), ('Vertical', 'Type'), ('Type', 'Type'), ('2X6P', 'Pin_Count'), ('2.0mm', 'Size'), ('Black', 'Color'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -8966,25 +8715,22 @@
           <t>RES1K01%1/10W0603</t>
         </is>
       </c>
-      <c r="AE84" t="n">
-        <v>1.285714285714286</v>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('1K', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9079,25 +8825,22 @@
           <t>RESR05%1/10W0603</t>
         </is>
       </c>
-      <c r="AE85" t="n">
-        <v>1.25</v>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('10W', 'Power'), ('5', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9192,25 +8935,22 @@
           <t>RESR221%1/2W1210</t>
         </is>
       </c>
-      <c r="AE86" t="n">
-        <v>1.272727272727273</v>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
         <is>
           <t>[('RES', 'Category'), (',', 'IGNORE'), ('0.22', 'Resistance'), ('Ω', 'Resistance'), ('1', 'Power'), ('/', 'Power'), ('2W', 'Power'), ('1', 'Tolerance'), ('%', 'Tolerance'), ('1210', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9315,25 +9055,22 @@
           <t>CAP105100V10%1206X7R</t>
         </is>
       </c>
-      <c r="AE87" t="n">
-        <v>1.222222222222222</v>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('1uF', 'Capacitance'), ('100V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('1206', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9436,25 +9173,22 @@
           <t>CAP47425V10%0603X7R</t>
         </is>
       </c>
-      <c r="AE88" t="n">
-        <v>1.206896551724138</v>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('0.47UF', 'Capacitance'), ('25V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9555,25 +9289,22 @@
           <t>CAP22425V10%0603X7R</t>
         </is>
       </c>
-      <c r="AE89" t="n">
-        <v>1.206896551724138</v>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('0.22uF', 'Capacitance'), ('(', 'IGNORE'), ('220nF', 'Capacitance'), (')', 'IGNORE'), ('25V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9646,25 +9377,22 @@
           <t>OTSOP-14</t>
         </is>
       </c>
-      <c r="AE90" t="n">
-        <v>0.5833333333333334</v>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('RT8462', 'O'), ('LED', 'Category'), ('Driver', 'Category'), ('Buck', 'O'), ('Boost', 'O'), ('SOP', 'Package'), ('-', 'Package'), ('14', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9737,25 +9465,22 @@
           <t>OTSOP-8</t>
         </is>
       </c>
-      <c r="AE91" t="n">
-        <v>0.4594594594594595</v>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('FAN7382', 'O'), ('GATE', 'O'), ('DRIVER', 'Category'), ('HI', 'O'), ('/', 'O'), ('LOW', 'O'), ('SIDE', 'O'), ('SOP', 'Package'), ('-', 'Package'), ('8', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9826,25 +9551,22 @@
           <t>OTSOP-16</t>
         </is>
       </c>
-      <c r="AE92" t="n">
-        <v>0.3947368421052632</v>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('FAN6920', 'O'), ('PWM', 'O'), ('CTLR', 'O'), ('PFC', 'O'), ('/', 'O'), ('QUASI', 'O'), ('-', 'O'), ('RES', 'Category'), ('SOP', 'Package'), ('-', 'Package'), ('16', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -9945,25 +9667,22 @@
           <t>CAP22550V10%0805X7R</t>
         </is>
       </c>
-      <c r="AE93" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('2.2uF', 'Capacitance'), ('50V', 'Voltage'), ('X7R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0805', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10040,25 +9759,22 @@
           <t>ICSO-14</t>
         </is>
       </c>
-      <c r="AE94" t="n">
-        <v>0.5185185185185185</v>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=7</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
-        <is>
-          <t>short_display20_len=7</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('LT1491', 'O'), ('QUAD', 'O'), ('OP', 'O'), ('-', 'O'), ('AMP', 'O'), ('SO', 'Package'), ('-', 'Package'), ('14', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10131,25 +9847,22 @@
           <t>OTJACK</t>
         </is>
       </c>
-      <c r="AE95" t="n">
-        <v>0.3636363636363636</v>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_3/15</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
-        <is>
-          <t>ner_low_valid_3/15</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('MODULAR', 'O'), ('JACK', 'Type'), ('8', 'O'), ('-', 'O'), ('8', 'O'), ('R', 'O'), ('/', 'O'), ('A', 'O'), ('UNSHLD', 'O'), ('/', 'O'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10250,25 +9963,22 @@
           <t>CAP22525V10%0603X5R</t>
         </is>
       </c>
-      <c r="AE96" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('2.2uF', 'Capacitance'), ('25V', 'Voltage'), ('X5R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10345,25 +10055,22 @@
           <t>OT11mm</t>
         </is>
       </c>
-      <c r="AE97" t="n">
-        <v>0.6226415094339622</v>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=6</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
-        <is>
-          <t>short_display20_len=6</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
         <is>
           <t>[('ENCODER', 'Category'), (',', 'IGNORE'), ('Rotary', 'O'), ('11mm', 'Size'), ('Vertical', 'Type'), ('with', 'O'), ('Push', 'Type'), ('-', 'O'), ('on', 'O'), ('Switch', 'Type'), ('and', 'O'), ('20', 'O'), ('clicks', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10444,25 +10151,22 @@
           <t>OT1x2P2.0mm</t>
         </is>
       </c>
-      <c r="AE98" t="n">
-        <v>0.6222222222222222</v>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
         <is>
           <t>[('CONN', 'Category'), (',', 'IGNORE'), ('Female', 'O'), ('Header', 'Category'), ('Straight', 'O'), ('1x2P', 'Pin_Count'), ('2.0mm', 'Size'), ('Black', 'Color'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10535,25 +10239,22 @@
           <t>OT</t>
         </is>
       </c>
-      <c r="AE99" t="n">
-        <v>0.8372093023255814</v>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>short_display20_len=2</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
-        <is>
-          <t>short_display20_len=2</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
         <is>
           <t>[('ENCODER', 'Category'), (',', 'IGNORE'), ('ED1112S', 'O'), ('F', 'O'), ('Type', 'Type'), ('N', 'Type'), ('=', 'Type'), ('7', 'Type'), ('Vertical', 'Type'), ('with', 'O'), ('Push', 'Type'), ('-', 'O'), ('on', 'O'), ('Switch', 'Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10662,25 +10363,22 @@
           <t>CAP22525V10%0603X5R</t>
         </is>
       </c>
-      <c r="AE100" t="n">
-        <v>1.214285714285714</v>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
         <is>
           <t>[('CAP', 'Category'), ('CER', 'Type'), (',', 'IGNORE'), ('2.2uF', 'Capacitance'), ('25V', 'Voltage'), ('X5R', 'Temp_Code'), ('10', 'Tolerance'), ('%', 'Tolerance'), ('0603', 'Package'), ('SMD', 'Process_Type'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10753,25 +10451,22 @@
           <t>OTSOP-14</t>
         </is>
       </c>
-      <c r="AE101" t="n">
-        <v>0.8378378378378378</v>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>duplicate_display_diff_pn</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
-        <is>
-          <t>duplicate_display_diff_pn</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
         <is>
           <t>[('IC', 'Category'), (',', 'IGNORE'), ('RT8475', 'O'), ('LED', 'Category'), ('Driver', 'Category'), ('Controller', 'Category'), ('SOP', 'Package'), ('-', 'Package'), ('14', 'Package'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
@@ -10844,25 +10539,22 @@
           <t>OT2.54mm</t>
         </is>
       </c>
-      <c r="AE102" t="n">
-        <v>0.3076923076923077</v>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>NEED_REVIEW</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>NEED_REVIEW</t>
+          <t>ner_low_valid_3/10</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
-        <is>
-          <t>ner_low_valid_3/10</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
         <is>
           <t>[('SW', 'Category'), (',', 'IGNORE'), ('SPST', 'O'), ('Gold', 'O'), ('Sealed', 'O'), ('3Positions', 'O'), ('2.54mm', 'Size'), ('DIP', 'O'), (',', 'IGNORE'), ('RoHS', 'Compliance')]</t>
         </is>
